--- a/CYP3A5_Allele_def_rs_excluidos.xlsx
+++ b/CYP3A5_Allele_def_rs_excluidos.xlsx
@@ -1,21 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
+    <sheet name="Filtrada " sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+  <si>
+    <t>rsID</t>
+  </si>
+  <si>
+    <t>rs41303343</t>
+  </si>
+  <si>
+    <t>CYP3A5 Allele</t>
+  </si>
+  <si>
+    <t>*1</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>*3</t>
+  </si>
+  <si>
+    <t>*6</t>
+  </si>
+  <si>
+    <t>*7</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>*8</t>
+  </si>
+  <si>
+    <t>*9</t>
+  </si>
+  <si>
+    <t>MAF European (non-finnish)</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Base  de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClinPGX </t>
+  </si>
+  <si>
+    <t>CYP3A5_frequency_table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs/*alelo </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -32,12 +94,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,22 +120,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +186,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +218,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +253,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,79 +429,129 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>rsID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>rs41303343</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CYP3A5 Allele</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>*1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>*3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>*6</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>*7</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>*8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>*9</t>
-        </is>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="5" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <f>SUM(C4)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
